--- a/docagent_clean_mvp/sample_data/raw_excels/ISO27001_SetA.xlsx
+++ b/docagent_clean_mvp/sample_data/raw_excels/ISO27001_SetA.xlsx
@@ -3084,7 +3084,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Network segmentation isolates production, staging, and corporate environments with documented firewall rulesets.</t>
+          <t>Standard Technological Controls policy mandates that network segmentation isolates production, staging, and corporate environments with documented firewall rulesets. [ISO27001-088]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Compliant - last firewall audit this quarter</t>
+          <t>Compliant - last reviewed this cycle</t>
         </is>
       </c>
     </row>
